--- a/Zinc/4. Exploratory data analysis/Normality_checks_log_vars.xlsx
+++ b/Zinc/4. Exploratory data analysis/Normality_checks_log_vars.xlsx
@@ -878,7 +878,7 @@
         <v>4</v>
       </c>
       <c r="C13" t="n">
-        <v>-1.12020373199102</v>
+        <v>-1.10737342678453</v>
       </c>
     </row>
     <row r="14">
@@ -889,7 +889,7 @@
         <v>4</v>
       </c>
       <c r="C14" t="n">
-        <v>0.0429748347748223</v>
+        <v>0.128973012708767</v>
       </c>
     </row>
     <row r="15">
@@ -900,7 +900,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>0.271832331148188</v>
+        <v>0.356286523315293</v>
       </c>
     </row>
     <row r="16">
@@ -911,7 +911,7 @@
         <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>-0.905615734133343</v>
+        <v>-0.841811795543959</v>
       </c>
     </row>
     <row r="17">
@@ -922,7 +922,7 @@
         <v>4</v>
       </c>
       <c r="C17" t="n">
-        <v>-1.36369499085423</v>
+        <v>-1.42300708957187</v>
       </c>
     </row>
     <row r="18">
@@ -933,7 +933,7 @@
         <v>4</v>
       </c>
       <c r="C18" t="n">
-        <v>-0.928807843824289</v>
+        <v>-0.989714753329462</v>
       </c>
     </row>
     <row r="19">
@@ -944,7 +944,7 @@
         <v>4</v>
       </c>
       <c r="C19" t="n">
-        <v>-0.800250537602769</v>
+        <v>-0.806430143601638</v>
       </c>
     </row>
     <row r="20">
@@ -955,7 +955,7 @@
         <v>4</v>
       </c>
       <c r="C20" t="n">
-        <v>-10.2016236673879</v>
+        <v>-10.6105025671191</v>
       </c>
     </row>
     <row r="21">
@@ -966,7 +966,7 @@
         <v>4</v>
       </c>
       <c r="C21" t="n">
-        <v>-0.364344820338342</v>
+        <v>-0.397512781930554</v>
       </c>
     </row>
     <row r="22">
@@ -977,7 +977,7 @@
         <v>4</v>
       </c>
       <c r="C22" t="n">
-        <v>-0.0972988817790461</v>
+        <v>-0.285849048571552</v>
       </c>
     </row>
     <row r="23">
@@ -988,7 +988,7 @@
         <v>4</v>
       </c>
       <c r="C23" t="n">
-        <v>-5.15266424928815</v>
+        <v>-5.15529936198532</v>
       </c>
     </row>
     <row r="24">
@@ -999,7 +999,7 @@
         <v>4</v>
       </c>
       <c r="C24" t="n">
-        <v>-0.0516409649725717</v>
+        <v>-0.0515887741729786</v>
       </c>
     </row>
     <row r="25">
@@ -1010,7 +1010,7 @@
         <v>4</v>
       </c>
       <c r="C25" t="n">
-        <v>-0.905567675288619</v>
+        <v>-0.896206680152932</v>
       </c>
     </row>
     <row r="26">
@@ -1021,7 +1021,7 @@
         <v>4</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.0725377021503263</v>
+        <v>-0.0721054340924363</v>
       </c>
     </row>
     <row r="27">
@@ -1032,7 +1032,7 @@
         <v>4</v>
       </c>
       <c r="C27" t="n">
-        <v>0.0678876718640013</v>
+        <v>0.159081565442412</v>
       </c>
     </row>
     <row r="28">
@@ -1043,7 +1043,7 @@
         <v>4</v>
       </c>
       <c r="C28" t="n">
-        <v>-3.27528734094303</v>
+        <v>-3.27976212727053</v>
       </c>
     </row>
     <row r="29">
@@ -1054,7 +1054,7 @@
         <v>4</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.558364529887108</v>
+        <v>-0.559052045890333</v>
       </c>
     </row>
     <row r="30">
@@ -1065,7 +1065,7 @@
         <v>4</v>
       </c>
       <c r="C30" t="n">
-        <v>0.0162390038844717</v>
+        <v>-0.0495663066554088</v>
       </c>
     </row>
     <row r="31">
@@ -1076,7 +1076,7 @@
         <v>4</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.40242974513814</v>
+        <v>-0.458005227708998</v>
       </c>
     </row>
     <row r="32">
@@ -1087,7 +1087,7 @@
         <v>4</v>
       </c>
       <c r="C32" t="n">
-        <v>-3.00023840702674</v>
+        <v>-3.00238235440687</v>
       </c>
     </row>
     <row r="33">
@@ -1098,7 +1098,7 @@
         <v>4</v>
       </c>
       <c r="C33" t="n">
-        <v>-1.61192251117383</v>
+        <v>-1.61179930443135</v>
       </c>
     </row>
     <row r="34">
@@ -1109,7 +1109,7 @@
         <v>4</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.824052124460312</v>
+        <v>-0.823376632115935</v>
       </c>
     </row>
     <row r="35">
@@ -1120,7 +1120,7 @@
         <v>4</v>
       </c>
       <c r="C35" t="n">
-        <v>-3.00777825197336</v>
+        <v>-3.01021885213896</v>
       </c>
     </row>
     <row r="36">
@@ -1131,7 +1131,7 @@
         <v>4</v>
       </c>
       <c r="C36" t="n">
-        <v>-1.80201824083318</v>
+        <v>-1.80355680759305</v>
       </c>
     </row>
     <row r="37">
@@ -1142,7 +1142,7 @@
         <v>4</v>
       </c>
       <c r="C37" t="n">
-        <v>-1.10518728237408</v>
+        <v>-1.1068994640977</v>
       </c>
     </row>
     <row r="38">
@@ -1153,7 +1153,7 @@
         <v>4</v>
       </c>
       <c r="C38" t="n">
-        <v>0.472399739915222</v>
+        <v>0.481678654742385</v>
       </c>
     </row>
     <row r="39">
@@ -1164,7 +1164,7 @@
         <v>4</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.127789383629942</v>
+        <v>-0.161032398788503</v>
       </c>
     </row>
     <row r="40">
@@ -1175,7 +1175,7 @@
         <v>6</v>
       </c>
       <c r="C40" t="n">
-        <v>0.143967540204244</v>
+        <v>0.161343293004364</v>
       </c>
     </row>
     <row r="41">
@@ -1186,7 +1186,7 @@
         <v>4</v>
       </c>
       <c r="C41" t="n">
-        <v>0.200393402783904</v>
+        <v>0.214383039830361</v>
       </c>
     </row>
     <row r="42">
@@ -1197,7 +1197,7 @@
         <v>4</v>
       </c>
       <c r="C42" t="n">
-        <v>0.353941376919049</v>
+        <v>0.367247619777316</v>
       </c>
     </row>
     <row r="43">
@@ -1208,7 +1208,7 @@
         <v>4</v>
       </c>
       <c r="C43" t="n">
-        <v>-0.979285573531401</v>
+        <v>-0.846494231875578</v>
       </c>
     </row>
     <row r="44">
@@ -1439,7 +1439,7 @@
         <v>4</v>
       </c>
       <c r="C64" t="n">
-        <v>-1.12020373199103</v>
+        <v>-1.10737342678453</v>
       </c>
     </row>
     <row r="65">
@@ -1450,7 +1450,7 @@
         <v>4</v>
       </c>
       <c r="C65" t="n">
-        <v>-1.12020373199102</v>
+        <v>-1.10737342678453</v>
       </c>
     </row>
     <row r="66">
@@ -1461,7 +1461,7 @@
         <v>4</v>
       </c>
       <c r="C66" t="n">
-        <v>0.0429748347748222</v>
+        <v>0.128973012708764</v>
       </c>
     </row>
     <row r="67">
@@ -1472,7 +1472,7 @@
         <v>4</v>
       </c>
       <c r="C67" t="n">
-        <v>0.042974834774822</v>
+        <v>0.128973012708764</v>
       </c>
     </row>
     <row r="68">
@@ -1483,7 +1483,7 @@
         <v>4</v>
       </c>
       <c r="C68" t="n">
-        <v>0.271832331148188</v>
+        <v>0.35628652331529</v>
       </c>
     </row>
     <row r="69">
@@ -1494,7 +1494,7 @@
         <v>4</v>
       </c>
       <c r="C69" t="n">
-        <v>0.271832331148188</v>
+        <v>0.356286523315291</v>
       </c>
     </row>
     <row r="70">
@@ -1505,7 +1505,7 @@
         <v>4</v>
       </c>
       <c r="C70" t="n">
-        <v>-0.905615734133343</v>
+        <v>-0.841811795543959</v>
       </c>
     </row>
     <row r="71">
@@ -1516,7 +1516,7 @@
         <v>4</v>
       </c>
       <c r="C71" t="n">
-        <v>-0.905615734133344</v>
+        <v>-0.841811795543959</v>
       </c>
     </row>
     <row r="72">
@@ -1527,7 +1527,7 @@
         <v>4</v>
       </c>
       <c r="C72" t="n">
-        <v>-1.36369499085423</v>
+        <v>-1.42300708957187</v>
       </c>
     </row>
     <row r="73">
@@ -1538,7 +1538,7 @@
         <v>4</v>
       </c>
       <c r="C73" t="n">
-        <v>-1.36369499085423</v>
+        <v>-1.42300708957187</v>
       </c>
     </row>
     <row r="74">
@@ -1549,7 +1549,7 @@
         <v>4</v>
       </c>
       <c r="C74" t="n">
-        <v>-0.928807843824295</v>
+        <v>-0.989714753329462</v>
       </c>
     </row>
     <row r="75">
@@ -1560,7 +1560,7 @@
         <v>4</v>
       </c>
       <c r="C75" t="n">
-        <v>-0.928807843824294</v>
+        <v>-0.989714753329462</v>
       </c>
     </row>
     <row r="76">
@@ -1571,7 +1571,7 @@
         <v>4</v>
       </c>
       <c r="C76" t="n">
-        <v>-0.800250537602765</v>
+        <v>-0.806430143601638</v>
       </c>
     </row>
     <row r="77">
@@ -1582,7 +1582,7 @@
         <v>4</v>
       </c>
       <c r="C77" t="n">
-        <v>-0.800250537602767</v>
+        <v>-0.806430143601638</v>
       </c>
     </row>
     <row r="78">
@@ -1593,7 +1593,7 @@
         <v>4</v>
       </c>
       <c r="C78" t="n">
-        <v>-10.2016236673713</v>
+        <v>-10.6105025671185</v>
       </c>
     </row>
     <row r="79">
@@ -1604,7 +1604,7 @@
         <v>4</v>
       </c>
       <c r="C79" t="n">
-        <v>-10.2016236673805</v>
+        <v>-10.6105025671212</v>
       </c>
     </row>
     <row r="80">
@@ -1615,7 +1615,7 @@
         <v>4</v>
       </c>
       <c r="C80" t="n">
-        <v>-0.364344820338343</v>
+        <v>-0.397512781930554</v>
       </c>
     </row>
     <row r="81">
@@ -1626,7 +1626,7 @@
         <v>4</v>
       </c>
       <c r="C81" t="n">
-        <v>-0.364344820338343</v>
+        <v>-0.397512781930554</v>
       </c>
     </row>
     <row r="82">
@@ -1637,7 +1637,7 @@
         <v>4</v>
       </c>
       <c r="C82" t="n">
-        <v>-3.27528734094303</v>
+        <v>-3.27976212727053</v>
       </c>
     </row>
     <row r="83">
@@ -1648,7 +1648,7 @@
         <v>4</v>
       </c>
       <c r="C83" t="n">
-        <v>-3.27528734094303</v>
+        <v>-3.27976212727054</v>
       </c>
     </row>
     <row r="84">
@@ -1659,7 +1659,7 @@
         <v>4</v>
       </c>
       <c r="C84" t="n">
-        <v>-0.558364529887108</v>
+        <v>-0.559052045890333</v>
       </c>
     </row>
     <row r="85">
@@ -1670,7 +1670,7 @@
         <v>4</v>
       </c>
       <c r="C85" t="n">
-        <v>-0.558364529887108</v>
+        <v>-0.559052045890336</v>
       </c>
     </row>
     <row r="86">
@@ -1681,7 +1681,7 @@
         <v>4</v>
       </c>
       <c r="C86" t="n">
-        <v>0.016239003884458</v>
+        <v>-0.0495663066553961</v>
       </c>
     </row>
     <row r="87">
@@ -1692,7 +1692,7 @@
         <v>4</v>
       </c>
       <c r="C87" t="n">
-        <v>0.016239003884458</v>
+        <v>-0.0495663066553964</v>
       </c>
     </row>
     <row r="88">
@@ -1703,7 +1703,7 @@
         <v>4</v>
       </c>
       <c r="C88" t="n">
-        <v>-0.402429745138139</v>
+        <v>-0.458005227708998</v>
       </c>
     </row>
     <row r="89">
@@ -1714,7 +1714,7 @@
         <v>4</v>
       </c>
       <c r="C89" t="n">
-        <v>-0.402429745138139</v>
+        <v>-0.458005227708999</v>
       </c>
     </row>
     <row r="90">
@@ -1725,7 +1725,7 @@
         <v>4</v>
       </c>
       <c r="C90" t="n">
-        <v>-3.00023840702674</v>
+        <v>-3.00238235440687</v>
       </c>
     </row>
     <row r="91">
@@ -1736,7 +1736,7 @@
         <v>4</v>
       </c>
       <c r="C91" t="n">
-        <v>-3.00023840702674</v>
+        <v>-3.00238235440687</v>
       </c>
     </row>
     <row r="92">
@@ -1747,7 +1747,7 @@
         <v>4</v>
       </c>
       <c r="C92" t="n">
-        <v>-1.61192251117382</v>
+        <v>-1.61179930443134</v>
       </c>
     </row>
     <row r="93">
@@ -1758,7 +1758,7 @@
         <v>4</v>
       </c>
       <c r="C93" t="n">
-        <v>-1.61192251117382</v>
+        <v>-1.61179930443134</v>
       </c>
     </row>
     <row r="94">
@@ -1769,7 +1769,7 @@
         <v>4</v>
       </c>
       <c r="C94" t="n">
-        <v>-0.824052124460315</v>
+        <v>-0.823376632115933</v>
       </c>
     </row>
     <row r="95">
@@ -1780,7 +1780,7 @@
         <v>4</v>
       </c>
       <c r="C95" t="n">
-        <v>-0.824052124460315</v>
+        <v>-0.823376632115932</v>
       </c>
     </row>
     <row r="96">
@@ -1791,7 +1791,7 @@
         <v>4</v>
       </c>
       <c r="C96" t="n">
-        <v>-3.00777825197336</v>
+        <v>-3.01021885213896</v>
       </c>
     </row>
     <row r="97">
@@ -1802,7 +1802,7 @@
         <v>4</v>
       </c>
       <c r="C97" t="n">
-        <v>-3.00777825197336</v>
+        <v>-3.01021885213896</v>
       </c>
     </row>
     <row r="98">
@@ -1813,7 +1813,7 @@
         <v>4</v>
       </c>
       <c r="C98" t="n">
-        <v>-1.80201824083318</v>
+        <v>-1.80355680759305</v>
       </c>
     </row>
     <row r="99">
@@ -1824,7 +1824,7 @@
         <v>4</v>
       </c>
       <c r="C99" t="n">
-        <v>-1.80201824083318</v>
+        <v>-1.80355680759305</v>
       </c>
     </row>
     <row r="100">
@@ -1835,7 +1835,7 @@
         <v>4</v>
       </c>
       <c r="C100" t="n">
-        <v>-1.10518728237408</v>
+        <v>-1.1068994640977</v>
       </c>
     </row>
     <row r="101">
@@ -1846,7 +1846,7 @@
         <v>4</v>
       </c>
       <c r="C101" t="n">
-        <v>-1.10518728237408</v>
+        <v>-1.1068994640977</v>
       </c>
     </row>
     <row r="102">
@@ -1857,7 +1857,7 @@
         <v>4</v>
       </c>
       <c r="C102" t="n">
-        <v>0.472399739915224</v>
+        <v>0.481678654742384</v>
       </c>
     </row>
     <row r="103">
@@ -1868,7 +1868,7 @@
         <v>4</v>
       </c>
       <c r="C103" t="n">
-        <v>0.472399739915225</v>
+        <v>0.481678654742384</v>
       </c>
     </row>
     <row r="104">
@@ -1879,7 +1879,7 @@
         <v>4</v>
       </c>
       <c r="C104" t="n">
-        <v>-0.127789383629939</v>
+        <v>-0.161032398788504</v>
       </c>
     </row>
     <row r="105">
@@ -1890,7 +1890,7 @@
         <v>4</v>
       </c>
       <c r="C105" t="n">
-        <v>-0.127789383629938</v>
+        <v>-0.161032398788503</v>
       </c>
     </row>
     <row r="106">
@@ -1901,7 +1901,7 @@
         <v>6</v>
       </c>
       <c r="C106" t="n">
-        <v>0.143967540204246</v>
+        <v>0.161343293004368</v>
       </c>
     </row>
     <row r="107">
@@ -1912,7 +1912,7 @@
         <v>6</v>
       </c>
       <c r="C107" t="n">
-        <v>0.143967540204248</v>
+        <v>0.161343293004368</v>
       </c>
     </row>
     <row r="108">
@@ -1923,7 +1923,7 @@
         <v>4</v>
       </c>
       <c r="C108" t="n">
-        <v>0.200393402783905</v>
+        <v>0.214383039830362</v>
       </c>
     </row>
     <row r="109">
@@ -1934,7 +1934,7 @@
         <v>4</v>
       </c>
       <c r="C109" t="n">
-        <v>0.200393402783904</v>
+        <v>0.214383039830361</v>
       </c>
     </row>
     <row r="110">
@@ -1945,7 +1945,7 @@
         <v>4</v>
       </c>
       <c r="C110" t="n">
-        <v>0.353941376919051</v>
+        <v>0.367247619777316</v>
       </c>
     </row>
     <row r="111">
@@ -1956,7 +1956,7 @@
         <v>4</v>
       </c>
       <c r="C111" t="n">
-        <v>0.35394137691905</v>
+        <v>0.367247619777316</v>
       </c>
     </row>
     <row r="112">
@@ -1967,7 +1967,7 @@
         <v>4</v>
       </c>
       <c r="C112" t="n">
-        <v>-0.979285573531397</v>
+        <v>-0.846494231875573</v>
       </c>
     </row>
     <row r="113">
@@ -1978,7 +1978,7 @@
         <v>4</v>
       </c>
       <c r="C113" t="n">
-        <v>-0.979285573531394</v>
+        <v>-0.846494231875572</v>
       </c>
     </row>
     <row r="114">
@@ -1989,7 +1989,7 @@
         <v>4</v>
       </c>
       <c r="C114" t="n">
-        <v>-0.0972988817790419</v>
+        <v>-0.285849048571561</v>
       </c>
     </row>
     <row r="115">
@@ -2000,7 +2000,7 @@
         <v>4</v>
       </c>
       <c r="C115" t="n">
-        <v>-0.0972988817790389</v>
+        <v>-0.285849048571562</v>
       </c>
     </row>
     <row r="116">
@@ -2011,7 +2011,7 @@
         <v>4</v>
       </c>
       <c r="C116" t="n">
-        <v>-5.15266424928814</v>
+        <v>-5.15529936198531</v>
       </c>
     </row>
     <row r="117">
@@ -2022,7 +2022,7 @@
         <v>4</v>
       </c>
       <c r="C117" t="n">
-        <v>-5.15266424928815</v>
+        <v>-5.1552993619853</v>
       </c>
     </row>
     <row r="118">
@@ -2033,7 +2033,7 @@
         <v>4</v>
       </c>
       <c r="C118" t="n">
-        <v>-0.0516409649725662</v>
+        <v>-0.0515887741729808</v>
       </c>
     </row>
     <row r="119">
@@ -2044,7 +2044,7 @@
         <v>4</v>
       </c>
       <c r="C119" t="n">
-        <v>-0.0516409649725663</v>
+        <v>-0.0515887741729778</v>
       </c>
     </row>
     <row r="120">
@@ -2055,7 +2055,7 @@
         <v>4</v>
       </c>
       <c r="C120" t="n">
-        <v>-0.90556767528862</v>
+        <v>-0.896206680152937</v>
       </c>
     </row>
     <row r="121">
@@ -2066,7 +2066,7 @@
         <v>4</v>
       </c>
       <c r="C121" t="n">
-        <v>-0.90556767528862</v>
+        <v>-0.896206680152933</v>
       </c>
     </row>
     <row r="122">
@@ -2077,7 +2077,7 @@
         <v>4</v>
       </c>
       <c r="C122" t="n">
-        <v>-0.07253770215033</v>
+        <v>-0.0721054340924443</v>
       </c>
     </row>
     <row r="123">
@@ -2088,7 +2088,7 @@
         <v>4</v>
       </c>
       <c r="C123" t="n">
-        <v>-0.0725377021503255</v>
+        <v>-0.0721054340924441</v>
       </c>
     </row>
     <row r="124">
@@ -2099,7 +2099,7 @@
         <v>4</v>
       </c>
       <c r="C124" t="n">
-        <v>0.0678876718639985</v>
+        <v>0.159081565442411</v>
       </c>
     </row>
     <row r="125">
@@ -2110,7 +2110,7 @@
         <v>4</v>
       </c>
       <c r="C125" t="n">
-        <v>0.0678876718640016</v>
+        <v>0.159081565442412</v>
       </c>
     </row>
     <row r="126">
@@ -2121,7 +2121,7 @@
         <v>4</v>
       </c>
       <c r="C126" t="n">
-        <v>-0.0859726730454351</v>
+        <v>-0.121043608477777</v>
       </c>
     </row>
     <row r="127">
@@ -2132,7 +2132,7 @@
         <v>4</v>
       </c>
       <c r="C127" t="n">
-        <v>-0.0859726730454328</v>
+        <v>-0.121043608477784</v>
       </c>
     </row>
     <row r="128">
@@ -2143,7 +2143,7 @@
         <v>4</v>
       </c>
       <c r="C128" t="n">
-        <v>-1.0051491783926</v>
+        <v>-0.933880752472261</v>
       </c>
     </row>
   </sheetData>

--- a/Zinc/4. Exploratory data analysis/Normality_checks_log_vars.xlsx
+++ b/Zinc/4. Exploratory data analysis/Normality_checks_log_vars.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="140">
   <si>
     <t xml:space="preserve">Variable</t>
   </si>
@@ -23,15 +23,12 @@
     <t xml:space="preserve">Skewness</t>
   </si>
   <si>
-    <t xml:space="preserve">Dist_from_EFPC_km</t>
+    <t xml:space="preserve">Upstream_from_main_stem_km</t>
   </si>
   <si>
     <t xml:space="preserve">Fail</t>
   </si>
   <si>
-    <t xml:space="preserve">Drainage_area_km2</t>
-  </si>
-  <si>
     <t xml:space="preserve">Temp_C</t>
   </si>
   <si>
@@ -428,10 +425,10 @@
     <t xml:space="preserve">TBL_Zn_nmol_g</t>
   </si>
   <si>
+    <t xml:space="preserve">TBL_Zn_umol_g</t>
+  </si>
+  <si>
     <t xml:space="preserve">TBL_Zn_mol_kg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TBL_Zn_umol_g</t>
   </si>
   <si>
     <t xml:space="preserve">rel_prop_Zn</t>
@@ -793,7 +790,7 @@
         <v>4</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.376279670926049</v>
+        <v>-1.17156887578643</v>
       </c>
     </row>
     <row r="4">
@@ -801,21 +798,21 @@
         <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C4" t="n">
-        <v>-1.17156887578643</v>
+        <v>0.0202703093038832</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0202703093038832</v>
+        <v>-2.60628412761065</v>
       </c>
     </row>
     <row r="6">
@@ -826,7 +823,7 @@
         <v>4</v>
       </c>
       <c r="C6" t="n">
-        <v>-2.60628412761065</v>
+        <v>-2.14837758124576</v>
       </c>
     </row>
     <row r="7">
@@ -837,7 +834,7 @@
         <v>4</v>
       </c>
       <c r="C7" t="n">
-        <v>-2.14837758124576</v>
+        <v>-0.314777301261375</v>
       </c>
     </row>
     <row r="8">
@@ -848,7 +845,7 @@
         <v>4</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.314777301261375</v>
+        <v>0.498547267692932</v>
       </c>
     </row>
     <row r="9">
@@ -859,7 +856,7 @@
         <v>4</v>
       </c>
       <c r="C9" t="n">
-        <v>0.498547267692932</v>
+        <v>-0.583713792211025</v>
       </c>
     </row>
     <row r="10">
@@ -870,7 +867,7 @@
         <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>-0.583713792211025</v>
+        <v>-0.492954851509791</v>
       </c>
     </row>
     <row r="11">
@@ -881,7 +878,7 @@
         <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>-0.492954851509791</v>
+        <v>-2.97254843865924</v>
       </c>
     </row>
     <row r="12">
@@ -892,7 +889,7 @@
         <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>-2.97254843865924</v>
+        <v>-1.21386134532828</v>
       </c>
     </row>
     <row r="13">
@@ -903,7 +900,7 @@
         <v>4</v>
       </c>
       <c r="C13" t="n">
-        <v>-1.21386134532828</v>
+        <v>-0.163037089395712</v>
       </c>
     </row>
     <row r="14">
@@ -914,7 +911,7 @@
         <v>4</v>
       </c>
       <c r="C14" t="n">
-        <v>-0.163037089395712</v>
+        <v>-1.12020373199102</v>
       </c>
     </row>
     <row r="15">
@@ -925,7 +922,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>-1.12020373199102</v>
+        <v>0.0429748347748223</v>
       </c>
     </row>
     <row r="16">
@@ -936,7 +933,7 @@
         <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>0.0429748347748223</v>
+        <v>0.271832331148188</v>
       </c>
     </row>
     <row r="17">
@@ -947,7 +944,7 @@
         <v>4</v>
       </c>
       <c r="C17" t="n">
-        <v>0.271832331148188</v>
+        <v>-0.905615734133343</v>
       </c>
     </row>
     <row r="18">
@@ -958,7 +955,7 @@
         <v>4</v>
       </c>
       <c r="C18" t="n">
-        <v>-0.905615734133343</v>
+        <v>-1.36369499085423</v>
       </c>
     </row>
     <row r="19">
@@ -969,7 +966,7 @@
         <v>4</v>
       </c>
       <c r="C19" t="n">
-        <v>-1.36369499085423</v>
+        <v>-0.928807843824289</v>
       </c>
     </row>
     <row r="20">
@@ -980,7 +977,7 @@
         <v>4</v>
       </c>
       <c r="C20" t="n">
-        <v>-0.928807843824289</v>
+        <v>-0.800250537602769</v>
       </c>
     </row>
     <row r="21">
@@ -991,7 +988,7 @@
         <v>4</v>
       </c>
       <c r="C21" t="n">
-        <v>-0.800250537602769</v>
+        <v>-10.2016236673879</v>
       </c>
     </row>
     <row r="22">
@@ -1002,7 +999,7 @@
         <v>4</v>
       </c>
       <c r="C22" t="n">
-        <v>-10.2016236673879</v>
+        <v>-0.364344820338342</v>
       </c>
     </row>
     <row r="23">
@@ -1013,7 +1010,7 @@
         <v>4</v>
       </c>
       <c r="C23" t="n">
-        <v>-0.364344820338342</v>
+        <v>-0.0972988817790461</v>
       </c>
     </row>
     <row r="24">
@@ -1024,7 +1021,7 @@
         <v>4</v>
       </c>
       <c r="C24" t="n">
-        <v>-0.0972988817790461</v>
+        <v>-5.15266424928815</v>
       </c>
     </row>
     <row r="25">
@@ -1035,7 +1032,7 @@
         <v>4</v>
       </c>
       <c r="C25" t="n">
-        <v>-5.15266424928815</v>
+        <v>-0.0516409649725717</v>
       </c>
     </row>
     <row r="26">
@@ -1046,7 +1043,7 @@
         <v>4</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.0516409649725717</v>
+        <v>-0.905567675288619</v>
       </c>
     </row>
     <row r="27">
@@ -1057,7 +1054,7 @@
         <v>4</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.905567675288619</v>
+        <v>-0.0725377021503263</v>
       </c>
     </row>
     <row r="28">
@@ -1068,7 +1065,7 @@
         <v>4</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.0725377021503263</v>
+        <v>0.0678876718640013</v>
       </c>
     </row>
     <row r="29">
@@ -1079,7 +1076,7 @@
         <v>4</v>
       </c>
       <c r="C29" t="n">
-        <v>0.0678876718640013</v>
+        <v>-3.27528734094303</v>
       </c>
     </row>
     <row r="30">
@@ -1090,7 +1087,7 @@
         <v>4</v>
       </c>
       <c r="C30" t="n">
-        <v>-3.27528734094303</v>
+        <v>-0.558364529887108</v>
       </c>
     </row>
     <row r="31">
@@ -1101,7 +1098,7 @@
         <v>4</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.558364529887108</v>
+        <v>0.0162390038844717</v>
       </c>
     </row>
     <row r="32">
@@ -1112,7 +1109,7 @@
         <v>4</v>
       </c>
       <c r="C32" t="n">
-        <v>0.0162390038844717</v>
+        <v>-0.40242974513814</v>
       </c>
     </row>
     <row r="33">
@@ -1123,7 +1120,7 @@
         <v>4</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.40242974513814</v>
+        <v>-3.00023840702674</v>
       </c>
     </row>
     <row r="34">
@@ -1134,7 +1131,7 @@
         <v>4</v>
       </c>
       <c r="C34" t="n">
-        <v>-3.00023840702674</v>
+        <v>-1.61192251117383</v>
       </c>
     </row>
     <row r="35">
@@ -1145,7 +1142,7 @@
         <v>4</v>
       </c>
       <c r="C35" t="n">
-        <v>-1.61192251117383</v>
+        <v>-0.824052124460312</v>
       </c>
     </row>
     <row r="36">
@@ -1156,7 +1153,7 @@
         <v>4</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.824052124460312</v>
+        <v>-3.00777825197336</v>
       </c>
     </row>
     <row r="37">
@@ -1167,7 +1164,7 @@
         <v>4</v>
       </c>
       <c r="C37" t="n">
-        <v>-3.00777825197336</v>
+        <v>-1.80201824083318</v>
       </c>
     </row>
     <row r="38">
@@ -1178,7 +1175,7 @@
         <v>4</v>
       </c>
       <c r="C38" t="n">
-        <v>-1.80201824083318</v>
+        <v>-1.10518728237408</v>
       </c>
     </row>
     <row r="39">
@@ -1189,7 +1186,7 @@
         <v>4</v>
       </c>
       <c r="C39" t="n">
-        <v>-1.10518728237408</v>
+        <v>0.472399739915222</v>
       </c>
     </row>
     <row r="40">
@@ -1200,7 +1197,7 @@
         <v>4</v>
       </c>
       <c r="C40" t="n">
-        <v>0.472399739915222</v>
+        <v>-0.127789383629942</v>
       </c>
     </row>
     <row r="41">
@@ -1208,10 +1205,10 @@
         <v>44</v>
       </c>
       <c r="B41" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.127789383629942</v>
+        <v>0.143967540204244</v>
       </c>
     </row>
     <row r="42">
@@ -1219,10 +1216,10 @@
         <v>45</v>
       </c>
       <c r="B42" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C42" t="n">
-        <v>0.143967540204244</v>
+        <v>0.200393402783904</v>
       </c>
     </row>
     <row r="43">
@@ -1233,7 +1230,7 @@
         <v>4</v>
       </c>
       <c r="C43" t="n">
-        <v>0.200393402783904</v>
+        <v>0.353941376919049</v>
       </c>
     </row>
     <row r="44">
@@ -1244,7 +1241,7 @@
         <v>4</v>
       </c>
       <c r="C44" t="n">
-        <v>0.353941376919049</v>
+        <v>-0.979285573531401</v>
       </c>
     </row>
     <row r="45">
@@ -1252,10 +1249,10 @@
         <v>48</v>
       </c>
       <c r="B45" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C45" t="n">
-        <v>-0.979285573531401</v>
+        <v>0.0202703093038834</v>
       </c>
     </row>
     <row r="46">
@@ -1263,10 +1260,10 @@
         <v>49</v>
       </c>
       <c r="B46" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C46" t="n">
-        <v>0.0202703093038834</v>
+        <v>0.0202703093038875</v>
       </c>
     </row>
     <row r="47">
@@ -1274,10 +1271,10 @@
         <v>50</v>
       </c>
       <c r="B47" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C47" t="n">
-        <v>0.0202703093038875</v>
+        <v>-2.60628412761065</v>
       </c>
     </row>
     <row r="48">
@@ -1299,7 +1296,7 @@
         <v>4</v>
       </c>
       <c r="C49" t="n">
-        <v>-2.60628412761065</v>
+        <v>-2.14837758124576</v>
       </c>
     </row>
     <row r="50">
@@ -1321,7 +1318,7 @@
         <v>4</v>
       </c>
       <c r="C51" t="n">
-        <v>-2.14837758124576</v>
+        <v>-0.314777301261378</v>
       </c>
     </row>
     <row r="52">
@@ -1332,7 +1329,7 @@
         <v>4</v>
       </c>
       <c r="C52" t="n">
-        <v>-0.314777301261378</v>
+        <v>-0.314777301261375</v>
       </c>
     </row>
     <row r="53">
@@ -1343,7 +1340,7 @@
         <v>4</v>
       </c>
       <c r="C53" t="n">
-        <v>-0.314777301261375</v>
+        <v>0.498547267692926</v>
       </c>
     </row>
     <row r="54">
@@ -1354,7 +1351,7 @@
         <v>4</v>
       </c>
       <c r="C54" t="n">
-        <v>0.498547267692926</v>
+        <v>0.498547267692927</v>
       </c>
     </row>
     <row r="55">
@@ -1365,7 +1362,7 @@
         <v>4</v>
       </c>
       <c r="C55" t="n">
-        <v>0.498547267692927</v>
+        <v>-0.583713792211029</v>
       </c>
     </row>
     <row r="56">
@@ -1376,7 +1373,7 @@
         <v>4</v>
       </c>
       <c r="C56" t="n">
-        <v>-0.583713792211029</v>
+        <v>-0.583713792211028</v>
       </c>
     </row>
     <row r="57">
@@ -1387,7 +1384,7 @@
         <v>4</v>
       </c>
       <c r="C57" t="n">
-        <v>-0.583713792211028</v>
+        <v>-0.492954851509791</v>
       </c>
     </row>
     <row r="58">
@@ -1398,7 +1395,7 @@
         <v>4</v>
       </c>
       <c r="C58" t="n">
-        <v>-0.492954851509791</v>
+        <v>-0.492954851509794</v>
       </c>
     </row>
     <row r="59">
@@ -1409,7 +1406,7 @@
         <v>4</v>
       </c>
       <c r="C59" t="n">
-        <v>-0.492954851509794</v>
+        <v>-2.97254843865924</v>
       </c>
     </row>
     <row r="60">
@@ -1431,7 +1428,7 @@
         <v>4</v>
       </c>
       <c r="C61" t="n">
-        <v>-2.97254843865924</v>
+        <v>-1.21386134532829</v>
       </c>
     </row>
     <row r="62">
@@ -1442,7 +1439,7 @@
         <v>4</v>
       </c>
       <c r="C62" t="n">
-        <v>-1.21386134532829</v>
+        <v>-1.21386134532828</v>
       </c>
     </row>
     <row r="63">
@@ -1453,7 +1450,7 @@
         <v>4</v>
       </c>
       <c r="C63" t="n">
-        <v>-1.21386134532828</v>
+        <v>-0.163037089395713</v>
       </c>
     </row>
     <row r="64">
@@ -1464,7 +1461,7 @@
         <v>4</v>
       </c>
       <c r="C64" t="n">
-        <v>-0.163037089395713</v>
+        <v>-0.163037089395712</v>
       </c>
     </row>
     <row r="65">
@@ -1475,7 +1472,7 @@
         <v>4</v>
       </c>
       <c r="C65" t="n">
-        <v>-0.163037089395712</v>
+        <v>-1.12020373199103</v>
       </c>
     </row>
     <row r="66">
@@ -1486,7 +1483,7 @@
         <v>4</v>
       </c>
       <c r="C66" t="n">
-        <v>-1.12020373199103</v>
+        <v>-1.12020373199102</v>
       </c>
     </row>
     <row r="67">
@@ -1497,7 +1494,7 @@
         <v>4</v>
       </c>
       <c r="C67" t="n">
-        <v>-1.12020373199102</v>
+        <v>0.0429748347748222</v>
       </c>
     </row>
     <row r="68">
@@ -1508,7 +1505,7 @@
         <v>4</v>
       </c>
       <c r="C68" t="n">
-        <v>0.0429748347748222</v>
+        <v>0.042974834774822</v>
       </c>
     </row>
     <row r="69">
@@ -1519,7 +1516,7 @@
         <v>4</v>
       </c>
       <c r="C69" t="n">
-        <v>0.042974834774822</v>
+        <v>0.271832331148188</v>
       </c>
     </row>
     <row r="70">
@@ -1541,7 +1538,7 @@
         <v>4</v>
       </c>
       <c r="C71" t="n">
-        <v>0.271832331148188</v>
+        <v>-0.905615734133343</v>
       </c>
     </row>
     <row r="72">
@@ -1552,7 +1549,7 @@
         <v>4</v>
       </c>
       <c r="C72" t="n">
-        <v>-0.905615734133343</v>
+        <v>-0.905615734133344</v>
       </c>
     </row>
     <row r="73">
@@ -1563,7 +1560,7 @@
         <v>4</v>
       </c>
       <c r="C73" t="n">
-        <v>-0.905615734133344</v>
+        <v>-1.36369499085423</v>
       </c>
     </row>
     <row r="74">
@@ -1585,7 +1582,7 @@
         <v>4</v>
       </c>
       <c r="C75" t="n">
-        <v>-1.36369499085423</v>
+        <v>-0.928807843824295</v>
       </c>
     </row>
     <row r="76">
@@ -1596,7 +1593,7 @@
         <v>4</v>
       </c>
       <c r="C76" t="n">
-        <v>-0.928807843824295</v>
+        <v>-0.928807843824294</v>
       </c>
     </row>
     <row r="77">
@@ -1607,7 +1604,7 @@
         <v>4</v>
       </c>
       <c r="C77" t="n">
-        <v>-0.928807843824294</v>
+        <v>-0.800250537602765</v>
       </c>
     </row>
     <row r="78">
@@ -1618,7 +1615,7 @@
         <v>4</v>
       </c>
       <c r="C78" t="n">
-        <v>-0.800250537602765</v>
+        <v>-0.800250537602767</v>
       </c>
     </row>
     <row r="79">
@@ -1629,7 +1626,7 @@
         <v>4</v>
       </c>
       <c r="C79" t="n">
-        <v>-0.800250537602767</v>
+        <v>-10.2016236673713</v>
       </c>
     </row>
     <row r="80">
@@ -1640,7 +1637,7 @@
         <v>4</v>
       </c>
       <c r="C80" t="n">
-        <v>-10.2016236673713</v>
+        <v>-10.2016236673805</v>
       </c>
     </row>
     <row r="81">
@@ -1651,7 +1648,7 @@
         <v>4</v>
       </c>
       <c r="C81" t="n">
-        <v>-10.2016236673805</v>
+        <v>-0.364344820338343</v>
       </c>
     </row>
     <row r="82">
@@ -1673,7 +1670,7 @@
         <v>4</v>
       </c>
       <c r="C83" t="n">
-        <v>-0.364344820338343</v>
+        <v>-3.27528734094303</v>
       </c>
     </row>
     <row r="84">
@@ -1695,7 +1692,7 @@
         <v>4</v>
       </c>
       <c r="C85" t="n">
-        <v>-3.27528734094303</v>
+        <v>-0.558364529887108</v>
       </c>
     </row>
     <row r="86">
@@ -1717,7 +1714,7 @@
         <v>4</v>
       </c>
       <c r="C87" t="n">
-        <v>-0.558364529887108</v>
+        <v>0.016239003884458</v>
       </c>
     </row>
     <row r="88">
@@ -1739,7 +1736,7 @@
         <v>4</v>
       </c>
       <c r="C89" t="n">
-        <v>0.016239003884458</v>
+        <v>-0.402429745138139</v>
       </c>
     </row>
     <row r="90">
@@ -1761,7 +1758,7 @@
         <v>4</v>
       </c>
       <c r="C91" t="n">
-        <v>-0.402429745138139</v>
+        <v>-3.00023840702674</v>
       </c>
     </row>
     <row r="92">
@@ -1783,7 +1780,7 @@
         <v>4</v>
       </c>
       <c r="C93" t="n">
-        <v>-3.00023840702674</v>
+        <v>-1.61192251117382</v>
       </c>
     </row>
     <row r="94">
@@ -1805,7 +1802,7 @@
         <v>4</v>
       </c>
       <c r="C95" t="n">
-        <v>-1.61192251117382</v>
+        <v>-0.824052124460315</v>
       </c>
     </row>
     <row r="96">
@@ -1827,7 +1824,7 @@
         <v>4</v>
       </c>
       <c r="C97" t="n">
-        <v>-0.824052124460315</v>
+        <v>-3.00777825197336</v>
       </c>
     </row>
     <row r="98">
@@ -1849,7 +1846,7 @@
         <v>4</v>
       </c>
       <c r="C99" t="n">
-        <v>-3.00777825197336</v>
+        <v>-1.80201824083318</v>
       </c>
     </row>
     <row r="100">
@@ -1871,7 +1868,7 @@
         <v>4</v>
       </c>
       <c r="C101" t="n">
-        <v>-1.80201824083318</v>
+        <v>-1.10518728237408</v>
       </c>
     </row>
     <row r="102">
@@ -1893,7 +1890,7 @@
         <v>4</v>
       </c>
       <c r="C103" t="n">
-        <v>-1.10518728237408</v>
+        <v>0.472399739915224</v>
       </c>
     </row>
     <row r="104">
@@ -1904,7 +1901,7 @@
         <v>4</v>
       </c>
       <c r="C104" t="n">
-        <v>0.472399739915224</v>
+        <v>0.472399739915225</v>
       </c>
     </row>
     <row r="105">
@@ -1915,7 +1912,7 @@
         <v>4</v>
       </c>
       <c r="C105" t="n">
-        <v>0.472399739915225</v>
+        <v>-0.127789383629939</v>
       </c>
     </row>
     <row r="106">
@@ -1926,7 +1923,7 @@
         <v>4</v>
       </c>
       <c r="C106" t="n">
-        <v>-0.127789383629939</v>
+        <v>-0.127789383629938</v>
       </c>
     </row>
     <row r="107">
@@ -1934,10 +1931,10 @@
         <v>110</v>
       </c>
       <c r="B107" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C107" t="n">
-        <v>-0.127789383629938</v>
+        <v>0.143967540204246</v>
       </c>
     </row>
     <row r="108">
@@ -1945,10 +1942,10 @@
         <v>111</v>
       </c>
       <c r="B108" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C108" t="n">
-        <v>0.143967540204246</v>
+        <v>0.143967540204248</v>
       </c>
     </row>
     <row r="109">
@@ -1956,10 +1953,10 @@
         <v>112</v>
       </c>
       <c r="B109" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C109" t="n">
-        <v>0.143967540204248</v>
+        <v>0.200393402783905</v>
       </c>
     </row>
     <row r="110">
@@ -1970,7 +1967,7 @@
         <v>4</v>
       </c>
       <c r="C110" t="n">
-        <v>0.200393402783905</v>
+        <v>0.200393402783904</v>
       </c>
     </row>
     <row r="111">
@@ -1981,7 +1978,7 @@
         <v>4</v>
       </c>
       <c r="C111" t="n">
-        <v>0.200393402783904</v>
+        <v>0.353941376919051</v>
       </c>
     </row>
     <row r="112">
@@ -1992,7 +1989,7 @@
         <v>4</v>
       </c>
       <c r="C112" t="n">
-        <v>0.353941376919051</v>
+        <v>0.35394137691905</v>
       </c>
     </row>
     <row r="113">
@@ -2003,7 +2000,7 @@
         <v>4</v>
       </c>
       <c r="C113" t="n">
-        <v>0.35394137691905</v>
+        <v>-0.979285573531397</v>
       </c>
     </row>
     <row r="114">
@@ -2014,7 +2011,7 @@
         <v>4</v>
       </c>
       <c r="C114" t="n">
-        <v>-0.979285573531397</v>
+        <v>-0.979285573531394</v>
       </c>
     </row>
     <row r="115">
@@ -2025,7 +2022,7 @@
         <v>4</v>
       </c>
       <c r="C115" t="n">
-        <v>-0.979285573531394</v>
+        <v>-0.0972988817790419</v>
       </c>
     </row>
     <row r="116">
@@ -2036,7 +2033,7 @@
         <v>4</v>
       </c>
       <c r="C116" t="n">
-        <v>-0.0972988817790419</v>
+        <v>-0.0972988817790389</v>
       </c>
     </row>
     <row r="117">
@@ -2047,7 +2044,7 @@
         <v>4</v>
       </c>
       <c r="C117" t="n">
-        <v>-0.0972988817790389</v>
+        <v>-0.0972988817790462</v>
       </c>
     </row>
     <row r="118">
@@ -2058,7 +2055,7 @@
         <v>4</v>
       </c>
       <c r="C118" t="n">
-        <v>-0.0972988817790462</v>
+        <v>-5.15266424928814</v>
       </c>
     </row>
     <row r="119">
@@ -2069,7 +2066,7 @@
         <v>4</v>
       </c>
       <c r="C119" t="n">
-        <v>-5.15266424928814</v>
+        <v>-5.15266424928815</v>
       </c>
     </row>
     <row r="120">
@@ -2080,7 +2077,7 @@
         <v>4</v>
       </c>
       <c r="C120" t="n">
-        <v>-5.15266424928815</v>
+        <v>-5.15266424928814</v>
       </c>
     </row>
     <row r="121">
@@ -2091,7 +2088,7 @@
         <v>4</v>
       </c>
       <c r="C121" t="n">
-        <v>-5.15266424928814</v>
+        <v>-0.0516409649725662</v>
       </c>
     </row>
     <row r="122">
@@ -2102,7 +2099,7 @@
         <v>4</v>
       </c>
       <c r="C122" t="n">
-        <v>-0.0516409649725662</v>
+        <v>-0.0516409649725663</v>
       </c>
     </row>
     <row r="123">
@@ -2113,7 +2110,7 @@
         <v>4</v>
       </c>
       <c r="C123" t="n">
-        <v>-0.0516409649725663</v>
+        <v>-0.0516409649725718</v>
       </c>
     </row>
     <row r="124">
@@ -2124,7 +2121,7 @@
         <v>4</v>
       </c>
       <c r="C124" t="n">
-        <v>-0.0516409649725718</v>
+        <v>-0.90556767528862</v>
       </c>
     </row>
     <row r="125">
@@ -2146,7 +2143,7 @@
         <v>4</v>
       </c>
       <c r="C126" t="n">
-        <v>-0.90556767528862</v>
+        <v>-0.905567675288621</v>
       </c>
     </row>
     <row r="127">
@@ -2157,7 +2154,7 @@
         <v>4</v>
       </c>
       <c r="C127" t="n">
-        <v>-0.905567675288621</v>
+        <v>-0.07253770215033</v>
       </c>
     </row>
     <row r="128">
@@ -2168,7 +2165,7 @@
         <v>4</v>
       </c>
       <c r="C128" t="n">
-        <v>-0.07253770215033</v>
+        <v>-0.0725377021503255</v>
       </c>
     </row>
     <row r="129">
@@ -2179,7 +2176,7 @@
         <v>4</v>
       </c>
       <c r="C129" t="n">
-        <v>-0.0725377021503255</v>
+        <v>-0.0725377021503258</v>
       </c>
     </row>
     <row r="130">
@@ -2190,7 +2187,7 @@
         <v>4</v>
       </c>
       <c r="C130" t="n">
-        <v>-0.0725377021503258</v>
+        <v>0.0678876718639985</v>
       </c>
     </row>
     <row r="131">
@@ -2201,7 +2198,7 @@
         <v>4</v>
       </c>
       <c r="C131" t="n">
-        <v>0.0678876718639985</v>
+        <v>0.0678876718640016</v>
       </c>
     </row>
     <row r="132">
@@ -2212,7 +2209,7 @@
         <v>4</v>
       </c>
       <c r="C132" t="n">
-        <v>0.0678876718640016</v>
+        <v>0.0678876718640013</v>
       </c>
     </row>
     <row r="133">
@@ -2223,7 +2220,7 @@
         <v>4</v>
       </c>
       <c r="C133" t="n">
-        <v>0.0678876718640013</v>
+        <v>-0.0859726730454351</v>
       </c>
     </row>
     <row r="134">
@@ -2234,7 +2231,7 @@
         <v>4</v>
       </c>
       <c r="C134" t="n">
-        <v>-0.0859726730454351</v>
+        <v>-0.085972673045433</v>
       </c>
     </row>
     <row r="135">
@@ -2256,17 +2253,6 @@
         <v>4</v>
       </c>
       <c r="C136" t="n">
-        <v>-0.085972673045433</v>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="s">
-        <v>140</v>
-      </c>
-      <c r="B137" t="s">
-        <v>4</v>
-      </c>
-      <c r="C137" t="n">
         <v>-1.0051491783926</v>
       </c>
     </row>

--- a/Zinc/4. Exploratory data analysis/Normality_checks_log_vars.xlsx
+++ b/Zinc/4. Exploratory data analysis/Normality_checks_log_vars.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="141">
   <si>
     <t xml:space="preserve">Variable</t>
   </si>
@@ -23,10 +23,13 @@
     <t xml:space="preserve">Skewness</t>
   </si>
   <si>
+    <t xml:space="preserve">Elevation_m</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fail</t>
+  </si>
+  <si>
     <t xml:space="preserve">Upstream_from_main_stem_km</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fail</t>
   </si>
   <si>
     <t xml:space="preserve">Temp_C</t>
@@ -779,7 +782,7 @@
         <v>4</v>
       </c>
       <c r="C2" t="n">
-        <v>-1.02708849855535</v>
+        <v>-0.320906267873043</v>
       </c>
     </row>
     <row r="3">
@@ -790,7 +793,7 @@
         <v>4</v>
       </c>
       <c r="C3" t="n">
-        <v>-1.17156887578643</v>
+        <v>-1.02708849855535</v>
       </c>
     </row>
     <row r="4">
@@ -798,21 +801,21 @@
         <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0202703093038832</v>
+        <v>-1.17156887578643</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" t="s">
         <v>8</v>
       </c>
-      <c r="B5" t="s">
-        <v>4</v>
-      </c>
       <c r="C5" t="n">
-        <v>-2.60628412761065</v>
+        <v>0.0202703093038832</v>
       </c>
     </row>
     <row r="6">
@@ -823,7 +826,7 @@
         <v>4</v>
       </c>
       <c r="C6" t="n">
-        <v>-2.14837758124576</v>
+        <v>-2.60628412761065</v>
       </c>
     </row>
     <row r="7">
@@ -834,7 +837,7 @@
         <v>4</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.314777301261375</v>
+        <v>-2.14837758124576</v>
       </c>
     </row>
     <row r="8">
@@ -845,7 +848,7 @@
         <v>4</v>
       </c>
       <c r="C8" t="n">
-        <v>0.498547267692932</v>
+        <v>-0.314777301261375</v>
       </c>
     </row>
     <row r="9">
@@ -856,7 +859,7 @@
         <v>4</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.583713792211025</v>
+        <v>0.498547267692932</v>
       </c>
     </row>
     <row r="10">
@@ -867,7 +870,7 @@
         <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>-0.492954851509791</v>
+        <v>-0.583713792211025</v>
       </c>
     </row>
     <row r="11">
@@ -878,7 +881,7 @@
         <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>-2.97254843865924</v>
+        <v>-0.492954851509791</v>
       </c>
     </row>
     <row r="12">
@@ -889,7 +892,7 @@
         <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>-1.21386134532828</v>
+        <v>-2.97254843865924</v>
       </c>
     </row>
     <row r="13">
@@ -900,7 +903,7 @@
         <v>4</v>
       </c>
       <c r="C13" t="n">
-        <v>-0.163037089395712</v>
+        <v>-1.21386134532828</v>
       </c>
     </row>
     <row r="14">
@@ -911,7 +914,7 @@
         <v>4</v>
       </c>
       <c r="C14" t="n">
-        <v>-1.12020373199102</v>
+        <v>-0.163037089395712</v>
       </c>
     </row>
     <row r="15">
@@ -922,7 +925,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>0.0429748347748223</v>
+        <v>-1.12020373199102</v>
       </c>
     </row>
     <row r="16">
@@ -933,7 +936,7 @@
         <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>0.271832331148188</v>
+        <v>0.0429748347748223</v>
       </c>
     </row>
     <row r="17">
@@ -944,7 +947,7 @@
         <v>4</v>
       </c>
       <c r="C17" t="n">
-        <v>-0.905615734133343</v>
+        <v>0.271832331148188</v>
       </c>
     </row>
     <row r="18">
@@ -955,7 +958,7 @@
         <v>4</v>
       </c>
       <c r="C18" t="n">
-        <v>-1.36369499085423</v>
+        <v>-0.905615734133343</v>
       </c>
     </row>
     <row r="19">
@@ -966,7 +969,7 @@
         <v>4</v>
       </c>
       <c r="C19" t="n">
-        <v>-0.928807843824289</v>
+        <v>-1.36369499085423</v>
       </c>
     </row>
     <row r="20">
@@ -977,7 +980,7 @@
         <v>4</v>
       </c>
       <c r="C20" t="n">
-        <v>-0.800250537602769</v>
+        <v>-0.928807843824289</v>
       </c>
     </row>
     <row r="21">
@@ -988,7 +991,7 @@
         <v>4</v>
       </c>
       <c r="C21" t="n">
-        <v>-10.2016236673879</v>
+        <v>-0.800250537602769</v>
       </c>
     </row>
     <row r="22">
@@ -999,7 +1002,7 @@
         <v>4</v>
       </c>
       <c r="C22" t="n">
-        <v>-0.364344820338342</v>
+        <v>-10.2016236673879</v>
       </c>
     </row>
     <row r="23">
@@ -1010,7 +1013,7 @@
         <v>4</v>
       </c>
       <c r="C23" t="n">
-        <v>-0.0972988817790461</v>
+        <v>-0.364344820338342</v>
       </c>
     </row>
     <row r="24">
@@ -1021,7 +1024,7 @@
         <v>4</v>
       </c>
       <c r="C24" t="n">
-        <v>-5.15266424928815</v>
+        <v>-0.0972988817790461</v>
       </c>
     </row>
     <row r="25">
@@ -1032,7 +1035,7 @@
         <v>4</v>
       </c>
       <c r="C25" t="n">
-        <v>-0.0516409649725717</v>
+        <v>-5.15266424928815</v>
       </c>
     </row>
     <row r="26">
@@ -1043,7 +1046,7 @@
         <v>4</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.905567675288619</v>
+        <v>-0.0516409649725717</v>
       </c>
     </row>
     <row r="27">
@@ -1054,7 +1057,7 @@
         <v>4</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.0725377021503263</v>
+        <v>-0.905567675288619</v>
       </c>
     </row>
     <row r="28">
@@ -1065,7 +1068,7 @@
         <v>4</v>
       </c>
       <c r="C28" t="n">
-        <v>0.0678876718640013</v>
+        <v>-0.0725377021503263</v>
       </c>
     </row>
     <row r="29">
@@ -1076,7 +1079,7 @@
         <v>4</v>
       </c>
       <c r="C29" t="n">
-        <v>-3.27528734094303</v>
+        <v>0.0678876718640013</v>
       </c>
     </row>
     <row r="30">
@@ -1087,7 +1090,7 @@
         <v>4</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.558364529887108</v>
+        <v>-3.27528734094303</v>
       </c>
     </row>
     <row r="31">
@@ -1098,7 +1101,7 @@
         <v>4</v>
       </c>
       <c r="C31" t="n">
-        <v>0.0162390038844717</v>
+        <v>-0.558364529887108</v>
       </c>
     </row>
     <row r="32">
@@ -1109,7 +1112,7 @@
         <v>4</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.40242974513814</v>
+        <v>0.0162390038844717</v>
       </c>
     </row>
     <row r="33">
@@ -1120,7 +1123,7 @@
         <v>4</v>
       </c>
       <c r="C33" t="n">
-        <v>-3.00023840702674</v>
+        <v>-0.40242974513814</v>
       </c>
     </row>
     <row r="34">
@@ -1131,7 +1134,7 @@
         <v>4</v>
       </c>
       <c r="C34" t="n">
-        <v>-1.61192251117383</v>
+        <v>-3.00023840702674</v>
       </c>
     </row>
     <row r="35">
@@ -1142,7 +1145,7 @@
         <v>4</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.824052124460312</v>
+        <v>-1.61192251117383</v>
       </c>
     </row>
     <row r="36">
@@ -1153,7 +1156,7 @@
         <v>4</v>
       </c>
       <c r="C36" t="n">
-        <v>-3.00777825197336</v>
+        <v>-0.824052124460312</v>
       </c>
     </row>
     <row r="37">
@@ -1164,7 +1167,7 @@
         <v>4</v>
       </c>
       <c r="C37" t="n">
-        <v>-1.80201824083318</v>
+        <v>-3.00777825197336</v>
       </c>
     </row>
     <row r="38">
@@ -1175,7 +1178,7 @@
         <v>4</v>
       </c>
       <c r="C38" t="n">
-        <v>-1.10518728237408</v>
+        <v>-1.80201824083318</v>
       </c>
     </row>
     <row r="39">
@@ -1186,7 +1189,7 @@
         <v>4</v>
       </c>
       <c r="C39" t="n">
-        <v>0.472399739915222</v>
+        <v>-1.10518728237408</v>
       </c>
     </row>
     <row r="40">
@@ -1197,7 +1200,7 @@
         <v>4</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.127789383629942</v>
+        <v>0.472399739915222</v>
       </c>
     </row>
     <row r="41">
@@ -1205,10 +1208,10 @@
         <v>44</v>
       </c>
       <c r="B41" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C41" t="n">
-        <v>0.143967540204244</v>
+        <v>-0.127789383629942</v>
       </c>
     </row>
     <row r="42">
@@ -1216,10 +1219,10 @@
         <v>45</v>
       </c>
       <c r="B42" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C42" t="n">
-        <v>0.200393402783904</v>
+        <v>0.143967540204244</v>
       </c>
     </row>
     <row r="43">
@@ -1230,7 +1233,7 @@
         <v>4</v>
       </c>
       <c r="C43" t="n">
-        <v>0.353941376919049</v>
+        <v>0.200393402783904</v>
       </c>
     </row>
     <row r="44">
@@ -1241,7 +1244,7 @@
         <v>4</v>
       </c>
       <c r="C44" t="n">
-        <v>-0.979285573531401</v>
+        <v>0.353941376919049</v>
       </c>
     </row>
     <row r="45">
@@ -1249,10 +1252,10 @@
         <v>48</v>
       </c>
       <c r="B45" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C45" t="n">
-        <v>0.0202703093038834</v>
+        <v>-0.979285573531401</v>
       </c>
     </row>
     <row r="46">
@@ -1260,10 +1263,10 @@
         <v>49</v>
       </c>
       <c r="B46" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C46" t="n">
-        <v>0.0202703093038875</v>
+        <v>0.0202703093038834</v>
       </c>
     </row>
     <row r="47">
@@ -1271,10 +1274,10 @@
         <v>50</v>
       </c>
       <c r="B47" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C47" t="n">
-        <v>-2.60628412761065</v>
+        <v>0.0202703093038875</v>
       </c>
     </row>
     <row r="48">
@@ -1296,7 +1299,7 @@
         <v>4</v>
       </c>
       <c r="C49" t="n">
-        <v>-2.14837758124576</v>
+        <v>-2.60628412761065</v>
       </c>
     </row>
     <row r="50">
@@ -1318,7 +1321,7 @@
         <v>4</v>
       </c>
       <c r="C51" t="n">
-        <v>-0.314777301261378</v>
+        <v>-2.14837758124576</v>
       </c>
     </row>
     <row r="52">
@@ -1329,7 +1332,7 @@
         <v>4</v>
       </c>
       <c r="C52" t="n">
-        <v>-0.314777301261375</v>
+        <v>-0.314777301261378</v>
       </c>
     </row>
     <row r="53">
@@ -1340,7 +1343,7 @@
         <v>4</v>
       </c>
       <c r="C53" t="n">
-        <v>0.498547267692926</v>
+        <v>-0.314777301261375</v>
       </c>
     </row>
     <row r="54">
@@ -1351,7 +1354,7 @@
         <v>4</v>
       </c>
       <c r="C54" t="n">
-        <v>0.498547267692927</v>
+        <v>0.498547267692926</v>
       </c>
     </row>
     <row r="55">
@@ -1362,7 +1365,7 @@
         <v>4</v>
       </c>
       <c r="C55" t="n">
-        <v>-0.583713792211029</v>
+        <v>0.498547267692927</v>
       </c>
     </row>
     <row r="56">
@@ -1373,7 +1376,7 @@
         <v>4</v>
       </c>
       <c r="C56" t="n">
-        <v>-0.583713792211028</v>
+        <v>-0.583713792211029</v>
       </c>
     </row>
     <row r="57">
@@ -1384,7 +1387,7 @@
         <v>4</v>
       </c>
       <c r="C57" t="n">
-        <v>-0.492954851509791</v>
+        <v>-0.583713792211028</v>
       </c>
     </row>
     <row r="58">
@@ -1395,7 +1398,7 @@
         <v>4</v>
       </c>
       <c r="C58" t="n">
-        <v>-0.492954851509794</v>
+        <v>-0.492954851509791</v>
       </c>
     </row>
     <row r="59">
@@ -1406,7 +1409,7 @@
         <v>4</v>
       </c>
       <c r="C59" t="n">
-        <v>-2.97254843865924</v>
+        <v>-0.492954851509794</v>
       </c>
     </row>
     <row r="60">
@@ -1428,7 +1431,7 @@
         <v>4</v>
       </c>
       <c r="C61" t="n">
-        <v>-1.21386134532829</v>
+        <v>-2.97254843865924</v>
       </c>
     </row>
     <row r="62">
@@ -1439,7 +1442,7 @@
         <v>4</v>
       </c>
       <c r="C62" t="n">
-        <v>-1.21386134532828</v>
+        <v>-1.21386134532829</v>
       </c>
     </row>
     <row r="63">
@@ -1450,7 +1453,7 @@
         <v>4</v>
       </c>
       <c r="C63" t="n">
-        <v>-0.163037089395713</v>
+        <v>-1.21386134532828</v>
       </c>
     </row>
     <row r="64">
@@ -1461,7 +1464,7 @@
         <v>4</v>
       </c>
       <c r="C64" t="n">
-        <v>-0.163037089395712</v>
+        <v>-0.163037089395713</v>
       </c>
     </row>
     <row r="65">
@@ -1472,7 +1475,7 @@
         <v>4</v>
       </c>
       <c r="C65" t="n">
-        <v>-1.12020373199103</v>
+        <v>-0.163037089395712</v>
       </c>
     </row>
     <row r="66">
@@ -1483,7 +1486,7 @@
         <v>4</v>
       </c>
       <c r="C66" t="n">
-        <v>-1.12020373199102</v>
+        <v>-1.12020373199103</v>
       </c>
     </row>
     <row r="67">
@@ -1494,7 +1497,7 @@
         <v>4</v>
       </c>
       <c r="C67" t="n">
-        <v>0.0429748347748222</v>
+        <v>-1.12020373199102</v>
       </c>
     </row>
     <row r="68">
@@ -1505,7 +1508,7 @@
         <v>4</v>
       </c>
       <c r="C68" t="n">
-        <v>0.042974834774822</v>
+        <v>0.0429748347748222</v>
       </c>
     </row>
     <row r="69">
@@ -1516,7 +1519,7 @@
         <v>4</v>
       </c>
       <c r="C69" t="n">
-        <v>0.271832331148188</v>
+        <v>0.042974834774822</v>
       </c>
     </row>
     <row r="70">
@@ -1538,7 +1541,7 @@
         <v>4</v>
       </c>
       <c r="C71" t="n">
-        <v>-0.905615734133343</v>
+        <v>0.271832331148188</v>
       </c>
     </row>
     <row r="72">
@@ -1549,7 +1552,7 @@
         <v>4</v>
       </c>
       <c r="C72" t="n">
-        <v>-0.905615734133344</v>
+        <v>-0.905615734133343</v>
       </c>
     </row>
     <row r="73">
@@ -1560,7 +1563,7 @@
         <v>4</v>
       </c>
       <c r="C73" t="n">
-        <v>-1.36369499085423</v>
+        <v>-0.905615734133344</v>
       </c>
     </row>
     <row r="74">
@@ -1582,7 +1585,7 @@
         <v>4</v>
       </c>
       <c r="C75" t="n">
-        <v>-0.928807843824295</v>
+        <v>-1.36369499085423</v>
       </c>
     </row>
     <row r="76">
@@ -1593,7 +1596,7 @@
         <v>4</v>
       </c>
       <c r="C76" t="n">
-        <v>-0.928807843824294</v>
+        <v>-0.928807843824295</v>
       </c>
     </row>
     <row r="77">
@@ -1604,7 +1607,7 @@
         <v>4</v>
       </c>
       <c r="C77" t="n">
-        <v>-0.800250537602765</v>
+        <v>-0.928807843824294</v>
       </c>
     </row>
     <row r="78">
@@ -1615,7 +1618,7 @@
         <v>4</v>
       </c>
       <c r="C78" t="n">
-        <v>-0.800250537602767</v>
+        <v>-0.800250537602765</v>
       </c>
     </row>
     <row r="79">
@@ -1626,7 +1629,7 @@
         <v>4</v>
       </c>
       <c r="C79" t="n">
-        <v>-10.2016236673713</v>
+        <v>-0.800250537602767</v>
       </c>
     </row>
     <row r="80">
@@ -1637,7 +1640,7 @@
         <v>4</v>
       </c>
       <c r="C80" t="n">
-        <v>-10.2016236673805</v>
+        <v>-10.2016236673713</v>
       </c>
     </row>
     <row r="81">
@@ -1648,7 +1651,7 @@
         <v>4</v>
       </c>
       <c r="C81" t="n">
-        <v>-0.364344820338343</v>
+        <v>-10.2016236673805</v>
       </c>
     </row>
     <row r="82">
@@ -1670,7 +1673,7 @@
         <v>4</v>
       </c>
       <c r="C83" t="n">
-        <v>-3.27528734094303</v>
+        <v>-0.364344820338343</v>
       </c>
     </row>
     <row r="84">
@@ -1692,7 +1695,7 @@
         <v>4</v>
       </c>
       <c r="C85" t="n">
-        <v>-0.558364529887108</v>
+        <v>-3.27528734094303</v>
       </c>
     </row>
     <row r="86">
@@ -1714,7 +1717,7 @@
         <v>4</v>
       </c>
       <c r="C87" t="n">
-        <v>0.016239003884458</v>
+        <v>-0.558364529887108</v>
       </c>
     </row>
     <row r="88">
@@ -1736,7 +1739,7 @@
         <v>4</v>
       </c>
       <c r="C89" t="n">
-        <v>-0.402429745138139</v>
+        <v>0.016239003884458</v>
       </c>
     </row>
     <row r="90">
@@ -1758,7 +1761,7 @@
         <v>4</v>
       </c>
       <c r="C91" t="n">
-        <v>-3.00023840702674</v>
+        <v>-0.402429745138139</v>
       </c>
     </row>
     <row r="92">
@@ -1780,7 +1783,7 @@
         <v>4</v>
       </c>
       <c r="C93" t="n">
-        <v>-1.61192251117382</v>
+        <v>-3.00023840702674</v>
       </c>
     </row>
     <row r="94">
@@ -1802,7 +1805,7 @@
         <v>4</v>
       </c>
       <c r="C95" t="n">
-        <v>-0.824052124460315</v>
+        <v>-1.61192251117382</v>
       </c>
     </row>
     <row r="96">
@@ -1824,7 +1827,7 @@
         <v>4</v>
       </c>
       <c r="C97" t="n">
-        <v>-3.00777825197336</v>
+        <v>-0.824052124460315</v>
       </c>
     </row>
     <row r="98">
@@ -1846,7 +1849,7 @@
         <v>4</v>
       </c>
       <c r="C99" t="n">
-        <v>-1.80201824083318</v>
+        <v>-3.00777825197336</v>
       </c>
     </row>
     <row r="100">
@@ -1868,7 +1871,7 @@
         <v>4</v>
       </c>
       <c r="C101" t="n">
-        <v>-1.10518728237408</v>
+        <v>-1.80201824083318</v>
       </c>
     </row>
     <row r="102">
@@ -1890,7 +1893,7 @@
         <v>4</v>
       </c>
       <c r="C103" t="n">
-        <v>0.472399739915224</v>
+        <v>-1.10518728237408</v>
       </c>
     </row>
     <row r="104">
@@ -1901,7 +1904,7 @@
         <v>4</v>
       </c>
       <c r="C104" t="n">
-        <v>0.472399739915225</v>
+        <v>0.472399739915224</v>
       </c>
     </row>
     <row r="105">
@@ -1912,7 +1915,7 @@
         <v>4</v>
       </c>
       <c r="C105" t="n">
-        <v>-0.127789383629939</v>
+        <v>0.472399739915225</v>
       </c>
     </row>
     <row r="106">
@@ -1923,7 +1926,7 @@
         <v>4</v>
       </c>
       <c r="C106" t="n">
-        <v>-0.127789383629938</v>
+        <v>-0.127789383629939</v>
       </c>
     </row>
     <row r="107">
@@ -1931,10 +1934,10 @@
         <v>110</v>
       </c>
       <c r="B107" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C107" t="n">
-        <v>0.143967540204246</v>
+        <v>-0.127789383629938</v>
       </c>
     </row>
     <row r="108">
@@ -1942,10 +1945,10 @@
         <v>111</v>
       </c>
       <c r="B108" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C108" t="n">
-        <v>0.143967540204248</v>
+        <v>0.143967540204246</v>
       </c>
     </row>
     <row r="109">
@@ -1953,10 +1956,10 @@
         <v>112</v>
       </c>
       <c r="B109" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C109" t="n">
-        <v>0.200393402783905</v>
+        <v>0.143967540204248</v>
       </c>
     </row>
     <row r="110">
@@ -1967,7 +1970,7 @@
         <v>4</v>
       </c>
       <c r="C110" t="n">
-        <v>0.200393402783904</v>
+        <v>0.200393402783905</v>
       </c>
     </row>
     <row r="111">
@@ -1978,7 +1981,7 @@
         <v>4</v>
       </c>
       <c r="C111" t="n">
-        <v>0.353941376919051</v>
+        <v>0.200393402783904</v>
       </c>
     </row>
     <row r="112">
@@ -1989,7 +1992,7 @@
         <v>4</v>
       </c>
       <c r="C112" t="n">
-        <v>0.35394137691905</v>
+        <v>0.353941376919051</v>
       </c>
     </row>
     <row r="113">
@@ -2000,7 +2003,7 @@
         <v>4</v>
       </c>
       <c r="C113" t="n">
-        <v>-0.979285573531397</v>
+        <v>0.35394137691905</v>
       </c>
     </row>
     <row r="114">
@@ -2011,7 +2014,7 @@
         <v>4</v>
       </c>
       <c r="C114" t="n">
-        <v>-0.979285573531394</v>
+        <v>-0.979285573531397</v>
       </c>
     </row>
     <row r="115">
@@ -2022,7 +2025,7 @@
         <v>4</v>
       </c>
       <c r="C115" t="n">
-        <v>-0.0972988817790419</v>
+        <v>-0.979285573531394</v>
       </c>
     </row>
     <row r="116">
@@ -2033,7 +2036,7 @@
         <v>4</v>
       </c>
       <c r="C116" t="n">
-        <v>-0.0972988817790389</v>
+        <v>-0.0972988817790419</v>
       </c>
     </row>
     <row r="117">
@@ -2044,7 +2047,7 @@
         <v>4</v>
       </c>
       <c r="C117" t="n">
-        <v>-0.0972988817790462</v>
+        <v>-0.0972988817790389</v>
       </c>
     </row>
     <row r="118">
@@ -2055,7 +2058,7 @@
         <v>4</v>
       </c>
       <c r="C118" t="n">
-        <v>-5.15266424928814</v>
+        <v>-0.0972988817790462</v>
       </c>
     </row>
     <row r="119">
@@ -2066,7 +2069,7 @@
         <v>4</v>
       </c>
       <c r="C119" t="n">
-        <v>-5.15266424928815</v>
+        <v>-5.15266424928814</v>
       </c>
     </row>
     <row r="120">
@@ -2077,7 +2080,7 @@
         <v>4</v>
       </c>
       <c r="C120" t="n">
-        <v>-5.15266424928814</v>
+        <v>-5.15266424928815</v>
       </c>
     </row>
     <row r="121">
@@ -2088,7 +2091,7 @@
         <v>4</v>
       </c>
       <c r="C121" t="n">
-        <v>-0.0516409649725662</v>
+        <v>-5.15266424928814</v>
       </c>
     </row>
     <row r="122">
@@ -2099,7 +2102,7 @@
         <v>4</v>
       </c>
       <c r="C122" t="n">
-        <v>-0.0516409649725663</v>
+        <v>-0.0516409649725662</v>
       </c>
     </row>
     <row r="123">
@@ -2110,7 +2113,7 @@
         <v>4</v>
       </c>
       <c r="C123" t="n">
-        <v>-0.0516409649725718</v>
+        <v>-0.0516409649725663</v>
       </c>
     </row>
     <row r="124">
@@ -2121,7 +2124,7 @@
         <v>4</v>
       </c>
       <c r="C124" t="n">
-        <v>-0.90556767528862</v>
+        <v>-0.0516409649725718</v>
       </c>
     </row>
     <row r="125">
@@ -2143,7 +2146,7 @@
         <v>4</v>
       </c>
       <c r="C126" t="n">
-        <v>-0.905567675288621</v>
+        <v>-0.90556767528862</v>
       </c>
     </row>
     <row r="127">
@@ -2154,7 +2157,7 @@
         <v>4</v>
       </c>
       <c r="C127" t="n">
-        <v>-0.07253770215033</v>
+        <v>-0.905567675288621</v>
       </c>
     </row>
     <row r="128">
@@ -2165,7 +2168,7 @@
         <v>4</v>
       </c>
       <c r="C128" t="n">
-        <v>-0.0725377021503255</v>
+        <v>-0.07253770215033</v>
       </c>
     </row>
     <row r="129">
@@ -2176,7 +2179,7 @@
         <v>4</v>
       </c>
       <c r="C129" t="n">
-        <v>-0.0725377021503258</v>
+        <v>-0.0725377021503255</v>
       </c>
     </row>
     <row r="130">
@@ -2187,7 +2190,7 @@
         <v>4</v>
       </c>
       <c r="C130" t="n">
-        <v>0.0678876718639985</v>
+        <v>-0.0725377021503258</v>
       </c>
     </row>
     <row r="131">
@@ -2198,7 +2201,7 @@
         <v>4</v>
       </c>
       <c r="C131" t="n">
-        <v>0.0678876718640016</v>
+        <v>0.0678876718639985</v>
       </c>
     </row>
     <row r="132">
@@ -2209,7 +2212,7 @@
         <v>4</v>
       </c>
       <c r="C132" t="n">
-        <v>0.0678876718640013</v>
+        <v>0.0678876718640016</v>
       </c>
     </row>
     <row r="133">
@@ -2220,7 +2223,7 @@
         <v>4</v>
       </c>
       <c r="C133" t="n">
-        <v>-0.0859726730454351</v>
+        <v>0.0678876718640013</v>
       </c>
     </row>
     <row r="134">
@@ -2231,7 +2234,7 @@
         <v>4</v>
       </c>
       <c r="C134" t="n">
-        <v>-0.085972673045433</v>
+        <v>-0.0859726730454351</v>
       </c>
     </row>
     <row r="135">
@@ -2242,7 +2245,7 @@
         <v>4</v>
       </c>
       <c r="C135" t="n">
-        <v>-0.0859726730454328</v>
+        <v>-0.085972673045433</v>
       </c>
     </row>
     <row r="136">
@@ -2253,6 +2256,17 @@
         <v>4</v>
       </c>
       <c r="C136" t="n">
+        <v>-0.0859726730454328</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="s">
+        <v>140</v>
+      </c>
+      <c r="B137" t="s">
+        <v>4</v>
+      </c>
+      <c r="C137" t="n">
         <v>-1.0051491783926</v>
       </c>
     </row>

--- a/Zinc/4. Exploratory data analysis/Normality_checks_log_vars.xlsx
+++ b/Zinc/4. Exploratory data analysis/Normality_checks_log_vars.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="144">
   <si>
     <t xml:space="preserve">Variable</t>
   </si>
@@ -158,7 +158,10 @@
     <t xml:space="preserve">TOrg_K_M</t>
   </si>
   <si>
-    <t xml:space="preserve">Zn_Toxicity_Daphnia_M</t>
+    <t xml:space="preserve">Zn_chronic_tox_M</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zn_acute_tox_M</t>
   </si>
   <si>
     <t xml:space="preserve">DOC_M</t>
@@ -365,10 +368,16 @@
     <t xml:space="preserve">TOrg_K_nM</t>
   </si>
   <si>
-    <t xml:space="preserve">Zn_Toxicity_Daphnia_uM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zn_Toxicity_Daphnia_nM</t>
+    <t xml:space="preserve">Zn_chronic_tox_uM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zn_chronic_tox_nM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zn_acute_tox_uM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zn_acute_tox_nM</t>
   </si>
   <si>
     <t xml:space="preserve">BL_Zn_nmol_kg</t>
@@ -1255,7 +1264,7 @@
         <v>4</v>
       </c>
       <c r="C45" t="n">
-        <v>-0.979285573531401</v>
+        <v>-0.615571887558176</v>
       </c>
     </row>
     <row r="46">
@@ -1263,10 +1272,10 @@
         <v>49</v>
       </c>
       <c r="B46" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C46" t="n">
-        <v>0.0202703093038834</v>
+        <v>-1.39538131001281</v>
       </c>
     </row>
     <row r="47">
@@ -1277,7 +1286,7 @@
         <v>8</v>
       </c>
       <c r="C47" t="n">
-        <v>0.0202703093038875</v>
+        <v>0.0202703093038834</v>
       </c>
     </row>
     <row r="48">
@@ -1285,10 +1294,10 @@
         <v>51</v>
       </c>
       <c r="B48" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C48" t="n">
-        <v>-2.60628412761065</v>
+        <v>0.0202703093038875</v>
       </c>
     </row>
     <row r="49">
@@ -1310,7 +1319,7 @@
         <v>4</v>
       </c>
       <c r="C50" t="n">
-        <v>-2.14837758124576</v>
+        <v>-2.60628412761065</v>
       </c>
     </row>
     <row r="51">
@@ -1332,7 +1341,7 @@
         <v>4</v>
       </c>
       <c r="C52" t="n">
-        <v>-0.314777301261378</v>
+        <v>-2.14837758124576</v>
       </c>
     </row>
     <row r="53">
@@ -1343,7 +1352,7 @@
         <v>4</v>
       </c>
       <c r="C53" t="n">
-        <v>-0.314777301261375</v>
+        <v>-0.314777301261378</v>
       </c>
     </row>
     <row r="54">
@@ -1354,7 +1363,7 @@
         <v>4</v>
       </c>
       <c r="C54" t="n">
-        <v>0.498547267692926</v>
+        <v>-0.314777301261375</v>
       </c>
     </row>
     <row r="55">
@@ -1365,7 +1374,7 @@
         <v>4</v>
       </c>
       <c r="C55" t="n">
-        <v>0.498547267692927</v>
+        <v>0.498547267692926</v>
       </c>
     </row>
     <row r="56">
@@ -1376,7 +1385,7 @@
         <v>4</v>
       </c>
       <c r="C56" t="n">
-        <v>-0.583713792211029</v>
+        <v>0.498547267692927</v>
       </c>
     </row>
     <row r="57">
@@ -1387,7 +1396,7 @@
         <v>4</v>
       </c>
       <c r="C57" t="n">
-        <v>-0.583713792211028</v>
+        <v>-0.583713792211029</v>
       </c>
     </row>
     <row r="58">
@@ -1398,7 +1407,7 @@
         <v>4</v>
       </c>
       <c r="C58" t="n">
-        <v>-0.492954851509791</v>
+        <v>-0.583713792211028</v>
       </c>
     </row>
     <row r="59">
@@ -1409,7 +1418,7 @@
         <v>4</v>
       </c>
       <c r="C59" t="n">
-        <v>-0.492954851509794</v>
+        <v>-0.492954851509791</v>
       </c>
     </row>
     <row r="60">
@@ -1420,7 +1429,7 @@
         <v>4</v>
       </c>
       <c r="C60" t="n">
-        <v>-2.97254843865924</v>
+        <v>-0.492954851509794</v>
       </c>
     </row>
     <row r="61">
@@ -1442,7 +1451,7 @@
         <v>4</v>
       </c>
       <c r="C62" t="n">
-        <v>-1.21386134532829</v>
+        <v>-2.97254843865924</v>
       </c>
     </row>
     <row r="63">
@@ -1453,7 +1462,7 @@
         <v>4</v>
       </c>
       <c r="C63" t="n">
-        <v>-1.21386134532828</v>
+        <v>-1.21386134532829</v>
       </c>
     </row>
     <row r="64">
@@ -1464,7 +1473,7 @@
         <v>4</v>
       </c>
       <c r="C64" t="n">
-        <v>-0.163037089395713</v>
+        <v>-1.21386134532828</v>
       </c>
     </row>
     <row r="65">
@@ -1475,7 +1484,7 @@
         <v>4</v>
       </c>
       <c r="C65" t="n">
-        <v>-0.163037089395712</v>
+        <v>-0.163037089395713</v>
       </c>
     </row>
     <row r="66">
@@ -1486,7 +1495,7 @@
         <v>4</v>
       </c>
       <c r="C66" t="n">
-        <v>-1.12020373199103</v>
+        <v>-0.163037089395712</v>
       </c>
     </row>
     <row r="67">
@@ -1497,7 +1506,7 @@
         <v>4</v>
       </c>
       <c r="C67" t="n">
-        <v>-1.12020373199102</v>
+        <v>-1.12020373199103</v>
       </c>
     </row>
     <row r="68">
@@ -1508,7 +1517,7 @@
         <v>4</v>
       </c>
       <c r="C68" t="n">
-        <v>0.0429748347748222</v>
+        <v>-1.12020373199102</v>
       </c>
     </row>
     <row r="69">
@@ -1519,7 +1528,7 @@
         <v>4</v>
       </c>
       <c r="C69" t="n">
-        <v>0.042974834774822</v>
+        <v>0.0429748347748222</v>
       </c>
     </row>
     <row r="70">
@@ -1530,7 +1539,7 @@
         <v>4</v>
       </c>
       <c r="C70" t="n">
-        <v>0.271832331148188</v>
+        <v>0.042974834774822</v>
       </c>
     </row>
     <row r="71">
@@ -1552,7 +1561,7 @@
         <v>4</v>
       </c>
       <c r="C72" t="n">
-        <v>-0.905615734133343</v>
+        <v>0.271832331148188</v>
       </c>
     </row>
     <row r="73">
@@ -1563,7 +1572,7 @@
         <v>4</v>
       </c>
       <c r="C73" t="n">
-        <v>-0.905615734133344</v>
+        <v>-0.905615734133343</v>
       </c>
     </row>
     <row r="74">
@@ -1574,7 +1583,7 @@
         <v>4</v>
       </c>
       <c r="C74" t="n">
-        <v>-1.36369499085423</v>
+        <v>-0.905615734133344</v>
       </c>
     </row>
     <row r="75">
@@ -1596,7 +1605,7 @@
         <v>4</v>
       </c>
       <c r="C76" t="n">
-        <v>-0.928807843824295</v>
+        <v>-1.36369499085423</v>
       </c>
     </row>
     <row r="77">
@@ -1607,7 +1616,7 @@
         <v>4</v>
       </c>
       <c r="C77" t="n">
-        <v>-0.928807843824294</v>
+        <v>-0.928807843824295</v>
       </c>
     </row>
     <row r="78">
@@ -1618,7 +1627,7 @@
         <v>4</v>
       </c>
       <c r="C78" t="n">
-        <v>-0.800250537602765</v>
+        <v>-0.928807843824294</v>
       </c>
     </row>
     <row r="79">
@@ -1629,7 +1638,7 @@
         <v>4</v>
       </c>
       <c r="C79" t="n">
-        <v>-0.800250537602767</v>
+        <v>-0.800250537602765</v>
       </c>
     </row>
     <row r="80">
@@ -1640,7 +1649,7 @@
         <v>4</v>
       </c>
       <c r="C80" t="n">
-        <v>-10.2016236673713</v>
+        <v>-0.800250537602767</v>
       </c>
     </row>
     <row r="81">
@@ -1651,7 +1660,7 @@
         <v>4</v>
       </c>
       <c r="C81" t="n">
-        <v>-10.2016236673805</v>
+        <v>-10.2016236673713</v>
       </c>
     </row>
     <row r="82">
@@ -1662,7 +1671,7 @@
         <v>4</v>
       </c>
       <c r="C82" t="n">
-        <v>-0.364344820338343</v>
+        <v>-10.2016236673805</v>
       </c>
     </row>
     <row r="83">
@@ -1684,7 +1693,7 @@
         <v>4</v>
       </c>
       <c r="C84" t="n">
-        <v>-3.27528734094303</v>
+        <v>-0.364344820338343</v>
       </c>
     </row>
     <row r="85">
@@ -1706,7 +1715,7 @@
         <v>4</v>
       </c>
       <c r="C86" t="n">
-        <v>-0.558364529887108</v>
+        <v>-3.27528734094303</v>
       </c>
     </row>
     <row r="87">
@@ -1728,7 +1737,7 @@
         <v>4</v>
       </c>
       <c r="C88" t="n">
-        <v>0.016239003884458</v>
+        <v>-0.558364529887108</v>
       </c>
     </row>
     <row r="89">
@@ -1750,7 +1759,7 @@
         <v>4</v>
       </c>
       <c r="C90" t="n">
-        <v>-0.402429745138139</v>
+        <v>0.016239003884458</v>
       </c>
     </row>
     <row r="91">
@@ -1772,7 +1781,7 @@
         <v>4</v>
       </c>
       <c r="C92" t="n">
-        <v>-3.00023840702674</v>
+        <v>-0.402429745138139</v>
       </c>
     </row>
     <row r="93">
@@ -1794,7 +1803,7 @@
         <v>4</v>
       </c>
       <c r="C94" t="n">
-        <v>-1.61192251117382</v>
+        <v>-3.00023840702674</v>
       </c>
     </row>
     <row r="95">
@@ -1816,7 +1825,7 @@
         <v>4</v>
       </c>
       <c r="C96" t="n">
-        <v>-0.824052124460315</v>
+        <v>-1.61192251117382</v>
       </c>
     </row>
     <row r="97">
@@ -1838,7 +1847,7 @@
         <v>4</v>
       </c>
       <c r="C98" t="n">
-        <v>-3.00777825197336</v>
+        <v>-0.824052124460315</v>
       </c>
     </row>
     <row r="99">
@@ -1860,7 +1869,7 @@
         <v>4</v>
       </c>
       <c r="C100" t="n">
-        <v>-1.80201824083318</v>
+        <v>-3.00777825197336</v>
       </c>
     </row>
     <row r="101">
@@ -1882,7 +1891,7 @@
         <v>4</v>
       </c>
       <c r="C102" t="n">
-        <v>-1.10518728237408</v>
+        <v>-1.80201824083318</v>
       </c>
     </row>
     <row r="103">
@@ -1904,7 +1913,7 @@
         <v>4</v>
       </c>
       <c r="C104" t="n">
-        <v>0.472399739915224</v>
+        <v>-1.10518728237408</v>
       </c>
     </row>
     <row r="105">
@@ -1915,7 +1924,7 @@
         <v>4</v>
       </c>
       <c r="C105" t="n">
-        <v>0.472399739915225</v>
+        <v>0.472399739915224</v>
       </c>
     </row>
     <row r="106">
@@ -1926,7 +1935,7 @@
         <v>4</v>
       </c>
       <c r="C106" t="n">
-        <v>-0.127789383629939</v>
+        <v>0.472399739915225</v>
       </c>
     </row>
     <row r="107">
@@ -1937,7 +1946,7 @@
         <v>4</v>
       </c>
       <c r="C107" t="n">
-        <v>-0.127789383629938</v>
+        <v>-0.127789383629939</v>
       </c>
     </row>
     <row r="108">
@@ -1945,10 +1954,10 @@
         <v>111</v>
       </c>
       <c r="B108" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C108" t="n">
-        <v>0.143967540204246</v>
+        <v>-0.127789383629938</v>
       </c>
     </row>
     <row r="109">
@@ -1959,7 +1968,7 @@
         <v>8</v>
       </c>
       <c r="C109" t="n">
-        <v>0.143967540204248</v>
+        <v>0.143967540204246</v>
       </c>
     </row>
     <row r="110">
@@ -1967,10 +1976,10 @@
         <v>113</v>
       </c>
       <c r="B110" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C110" t="n">
-        <v>0.200393402783905</v>
+        <v>0.143967540204248</v>
       </c>
     </row>
     <row r="111">
@@ -1981,7 +1990,7 @@
         <v>4</v>
       </c>
       <c r="C111" t="n">
-        <v>0.200393402783904</v>
+        <v>0.200393402783905</v>
       </c>
     </row>
     <row r="112">
@@ -1992,7 +2001,7 @@
         <v>4</v>
       </c>
       <c r="C112" t="n">
-        <v>0.353941376919051</v>
+        <v>0.200393402783904</v>
       </c>
     </row>
     <row r="113">
@@ -2003,7 +2012,7 @@
         <v>4</v>
       </c>
       <c r="C113" t="n">
-        <v>0.35394137691905</v>
+        <v>0.353941376919051</v>
       </c>
     </row>
     <row r="114">
@@ -2014,7 +2023,7 @@
         <v>4</v>
       </c>
       <c r="C114" t="n">
-        <v>-0.979285573531397</v>
+        <v>0.35394137691905</v>
       </c>
     </row>
     <row r="115">
@@ -2025,7 +2034,7 @@
         <v>4</v>
       </c>
       <c r="C115" t="n">
-        <v>-0.979285573531394</v>
+        <v>-0.61557188755817</v>
       </c>
     </row>
     <row r="116">
@@ -2036,7 +2045,7 @@
         <v>4</v>
       </c>
       <c r="C116" t="n">
-        <v>-0.0972988817790419</v>
+        <v>-0.61557188755817</v>
       </c>
     </row>
     <row r="117">
@@ -2047,7 +2056,7 @@
         <v>4</v>
       </c>
       <c r="C117" t="n">
-        <v>-0.0972988817790389</v>
+        <v>-1.39538131001282</v>
       </c>
     </row>
     <row r="118">
@@ -2058,7 +2067,7 @@
         <v>4</v>
       </c>
       <c r="C118" t="n">
-        <v>-0.0972988817790462</v>
+        <v>-1.39538131001282</v>
       </c>
     </row>
     <row r="119">
@@ -2069,7 +2078,7 @@
         <v>4</v>
       </c>
       <c r="C119" t="n">
-        <v>-5.15266424928814</v>
+        <v>-0.0972988817790419</v>
       </c>
     </row>
     <row r="120">
@@ -2080,7 +2089,7 @@
         <v>4</v>
       </c>
       <c r="C120" t="n">
-        <v>-5.15266424928815</v>
+        <v>-0.0972988817790389</v>
       </c>
     </row>
     <row r="121">
@@ -2091,7 +2100,7 @@
         <v>4</v>
       </c>
       <c r="C121" t="n">
-        <v>-5.15266424928814</v>
+        <v>-0.0972988817790462</v>
       </c>
     </row>
     <row r="122">
@@ -2102,7 +2111,7 @@
         <v>4</v>
       </c>
       <c r="C122" t="n">
-        <v>-0.0516409649725662</v>
+        <v>-5.15266424928814</v>
       </c>
     </row>
     <row r="123">
@@ -2113,7 +2122,7 @@
         <v>4</v>
       </c>
       <c r="C123" t="n">
-        <v>-0.0516409649725663</v>
+        <v>-5.15266424928815</v>
       </c>
     </row>
     <row r="124">
@@ -2124,7 +2133,7 @@
         <v>4</v>
       </c>
       <c r="C124" t="n">
-        <v>-0.0516409649725718</v>
+        <v>-5.15266424928814</v>
       </c>
     </row>
     <row r="125">
@@ -2135,7 +2144,7 @@
         <v>4</v>
       </c>
       <c r="C125" t="n">
-        <v>-0.90556767528862</v>
+        <v>-0.0516409649725662</v>
       </c>
     </row>
     <row r="126">
@@ -2146,7 +2155,7 @@
         <v>4</v>
       </c>
       <c r="C126" t="n">
-        <v>-0.90556767528862</v>
+        <v>-0.0516409649725663</v>
       </c>
     </row>
     <row r="127">
@@ -2157,7 +2166,7 @@
         <v>4</v>
       </c>
       <c r="C127" t="n">
-        <v>-0.905567675288621</v>
+        <v>-0.0516409649725718</v>
       </c>
     </row>
     <row r="128">
@@ -2168,7 +2177,7 @@
         <v>4</v>
       </c>
       <c r="C128" t="n">
-        <v>-0.07253770215033</v>
+        <v>-0.90556767528862</v>
       </c>
     </row>
     <row r="129">
@@ -2179,7 +2188,7 @@
         <v>4</v>
       </c>
       <c r="C129" t="n">
-        <v>-0.0725377021503255</v>
+        <v>-0.90556767528862</v>
       </c>
     </row>
     <row r="130">
@@ -2190,7 +2199,7 @@
         <v>4</v>
       </c>
       <c r="C130" t="n">
-        <v>-0.0725377021503258</v>
+        <v>-0.905567675288621</v>
       </c>
     </row>
     <row r="131">
@@ -2201,7 +2210,7 @@
         <v>4</v>
       </c>
       <c r="C131" t="n">
-        <v>0.0678876718639985</v>
+        <v>-0.07253770215033</v>
       </c>
     </row>
     <row r="132">
@@ -2212,7 +2221,7 @@
         <v>4</v>
       </c>
       <c r="C132" t="n">
-        <v>0.0678876718640016</v>
+        <v>-0.0725377021503255</v>
       </c>
     </row>
     <row r="133">
@@ -2223,7 +2232,7 @@
         <v>4</v>
       </c>
       <c r="C133" t="n">
-        <v>0.0678876718640013</v>
+        <v>-0.0725377021503258</v>
       </c>
     </row>
     <row r="134">
@@ -2234,7 +2243,7 @@
         <v>4</v>
       </c>
       <c r="C134" t="n">
-        <v>-0.0859726730454351</v>
+        <v>0.0678876718639985</v>
       </c>
     </row>
     <row r="135">
@@ -2245,7 +2254,7 @@
         <v>4</v>
       </c>
       <c r="C135" t="n">
-        <v>-0.085972673045433</v>
+        <v>0.0678876718640016</v>
       </c>
     </row>
     <row r="136">
@@ -2256,7 +2265,7 @@
         <v>4</v>
       </c>
       <c r="C136" t="n">
-        <v>-0.0859726730454328</v>
+        <v>0.0678876718640013</v>
       </c>
     </row>
     <row r="137">
@@ -2267,6 +2276,39 @@
         <v>4</v>
       </c>
       <c r="C137" t="n">
+        <v>-0.0859726730454351</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="s">
+        <v>141</v>
+      </c>
+      <c r="B138" t="s">
+        <v>4</v>
+      </c>
+      <c r="C138" t="n">
+        <v>-0.085972673045433</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="s">
+        <v>142</v>
+      </c>
+      <c r="B139" t="s">
+        <v>4</v>
+      </c>
+      <c r="C139" t="n">
+        <v>-0.0859726730454328</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="s">
+        <v>143</v>
+      </c>
+      <c r="B140" t="s">
+        <v>4</v>
+      </c>
+      <c r="C140" t="n">
         <v>-1.0051491783926</v>
       </c>
     </row>
